--- a/Documentatie/Verslagen/ObjectDetectionModelResearchTable.xlsx
+++ b/Documentatie/Verslagen/ObjectDetectionModelResearchTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/518c28196cba6f70/Documenten/GitHub/SDC-TFF-Project7-8/Documentatie/Verslagen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{968AD4E2-7281-4FFD-A457-365E7A3A9BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{968AD4E2-7281-4FFD-A457-365E7A3A9BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E02CCD-876A-44B8-8E42-E71318A1FF2A}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{477A8081-41AD-42FF-8C14-0FDD8409DF53}"/>
+    <workbookView xWindow="11895" yWindow="0" windowWidth="17010" windowHeight="15585" xr2:uid="{477A8081-41AD-42FF-8C14-0FDD8409DF53}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
-  <si>
-    <t>Criterium 1: Latency</t>
-  </si>
-  <si>
-    <t>Criterium 2: Accuracy</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
   <si>
     <t>Criterium 3: Load</t>
   </si>
@@ -113,15 +107,9 @@
     <t>Resultaat</t>
   </si>
   <si>
-    <t>~10-25 ms</t>
-  </si>
-  <si>
     <t>~100-200 ms</t>
   </si>
   <si>
-    <t>~25-50 ms</t>
-  </si>
-  <si>
     <t>Simple</t>
   </si>
   <si>
@@ -131,18 +119,12 @@
     <t>High</t>
   </si>
   <si>
-    <t>Very High</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
     <t>Low/Medium</t>
   </si>
   <si>
-    <t>~30-40 ms</t>
-  </si>
-  <si>
     <t>Scorebord</t>
   </si>
   <si>
@@ -177,16 +159,84 @@
   </si>
   <si>
     <t>&gt;= 101 ms</t>
+  </si>
+  <si>
+    <t>https://docs.ultralytics.com/models/yolo26/#overview</t>
+  </si>
+  <si>
+    <t>Faster RCNN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://huggingface.co/sjatin352/faster_rcnn_resnet50_genetic_algorithm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kaggle.com/code/abedi756/ssd-single-shot-detection#Load-in-the-model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://arxiv.org/pdf/1512.02325 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.ultralytics.com/models/yolov8/#overview </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.readytensor.ai/publications/comparing-yolov8-ssd-and-fasterrcnn-for-realtime-object-detection-IbA4gAvuaYW8 </t>
+  </si>
+  <si>
+    <t>Criterium 2: Accuracy (mAP)</t>
+  </si>
+  <si>
+    <t>Criterium 1: Latency (ms)</t>
+  </si>
+  <si>
+    <t>~70-90%</t>
+  </si>
+  <si>
+    <t>~75-90%</t>
+  </si>
+  <si>
+    <t>~72-74%</t>
+  </si>
+  <si>
+    <t>80-95%</t>
+  </si>
+  <si>
+    <t>~10-33 ms</t>
+  </si>
+  <si>
+    <t>~8-40 ms</t>
+  </si>
+  <si>
+    <t>~17-33 ms</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>70-80%</t>
+  </si>
+  <si>
+    <t>81-90%</t>
+  </si>
+  <si>
+    <t>91-100%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -209,14 +259,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -230,6 +283,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,8 +641,8 @@
   <dimension ref="B2:P19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
@@ -601,106 +658,106 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -708,31 +765,31 @@
     </row>
     <row r="6" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -740,31 +797,31 @@
     </row>
     <row r="7" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>1.5</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>1.5</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -772,31 +829,31 @@
     </row>
     <row r="8" spans="2:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -804,7 +861,7 @@
     </row>
     <row r="9" spans="2:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <f>SUM((C5*E5)+(C6*E6)+(C7*E7)+(C8*E8))</f>
@@ -812,108 +869,156 @@
       </c>
       <c r="G9">
         <f>SUM((C5*G5)+(C6*G6)+(C7*G7)+(C8*G8))</f>
-        <v>22.5</v>
+        <v>20.7</v>
       </c>
       <c r="I9">
         <f>SUM((C5*I5)+(C6*I6)+(C7*I7)+(C8*I8))</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K9">
         <f>SUM((C5*K5)+(C6*K6)+(C7*K7)+(C8*K8))</f>
         <v>13</v>
       </c>
     </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="M13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="M14" t="s">
-        <v>13</v>
-      </c>
-      <c r="N14" t="s">
-        <v>14</v>
-      </c>
-      <c r="O14" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="N15" t="s">
+      <c r="P15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" t="s">
         <v>40</v>
-      </c>
-      <c r="O15" t="s">
-        <v>41</v>
-      </c>
-      <c r="P15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="M16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" t="s">
-        <v>45</v>
-      </c>
-      <c r="P16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N17" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="P17" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O18" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="P18" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M19" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="P19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E12" r:id="rId1" location="overview" xr:uid="{A04A9BE7-4E6A-44D4-99E9-D7C0DC70F282}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{677C0D33-2609-4930-B8F6-7D14E2764BD1}"/>
+    <hyperlink ref="E15" r:id="rId3" location="Load-in-the-model " xr:uid="{8882E08D-BAE4-42D4-99A3-7DA3CB433F3B}"/>
+    <hyperlink ref="E16" r:id="rId4" xr:uid="{CEE64DB3-5EAB-4872-9A91-B41F5AF975FD}"/>
+    <hyperlink ref="E11" r:id="rId5" location="overview " xr:uid="{DE74D5BF-F616-4567-8A56-EE2A9F36E83D}"/>
+    <hyperlink ref="E14" r:id="rId6" xr:uid="{1DD31506-5F37-428B-89C4-B0F157A82E22}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>